--- a/artfynd/A 42783-2023 artfynd.xlsx
+++ b/artfynd/A 42783-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42783-2023 artfynd.xlsx
+++ b/artfynd/A 42783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103480512</v>
+        <v>103480403</v>
       </c>
       <c r="B2" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Sjötåtel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Deschampsia setacea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(Huds.) Hack.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447056.7306139437</v>
+        <v>447007</v>
       </c>
       <c r="R2" t="n">
-        <v>6282115.073895555</v>
+        <v>6282276</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,24 +759,14 @@
           <t>2022-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På basen av videbuske</t>
+          <t>Strand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,6 +791,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>103480512</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>530</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Möckeln, Rönnäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>447057</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6282115</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Agunnaryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På basen av videbuske</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42783-2023 artfynd.xlsx
+++ b/artfynd/A 42783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103480403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,8 +920,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103480512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>